--- a/out/LSTM-S4_repeat_3_000008.xlsx
+++ b/out/LSTM-S4_repeat_3_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.462243845257878</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.462243845257878</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.386393030374176</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8622438452578778</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8622438452578778</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001316227959683165</v>
+        <v>-8.908517028472852e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1512093120794342</v>
+        <v>-0.1023417502729988</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1514554797617658</v>
+        <v>-0.1025097581408063</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4118773248406163</v>
+        <v>0.2837880463890378</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6730899894655917</v>
+        <v>0.4656112180782985</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02934613633254492</v>
+        <v>0.02021983872223807</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3192443141875116</v>
+        <v>0.2218076219583314</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05146312427903974</v>
+        <v>0.03545857947315587</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3928148166683598</v>
+        <v>0.272498451292105</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06252193003882106</v>
+        <v>0.04307829822141423</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4663903990595937</v>
+        <v>0.3231928376953367</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01654486918756538</v>
+        <v>0.0113993390061749</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4368783834454406</v>
+        <v>0.3028586413121533</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009191027858687134</v>
+        <v>0.006331256169607655</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4387003097358528</v>
+        <v>0.3041124318635659</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01931219112348164</v>
+        <v>0.01330510269712677</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4681450155157126</v>
+        <v>0.3243998215040392</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007583587329954639</v>
+        <v>0.005224415909789999</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.463984703571344</v>
+        <v>0.32153155804156</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005399221778498081</v>
+        <v>0.003719134956839246</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4671969123559822</v>
+        <v>0.3237432331153297</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002122815508591047</v>
+        <v>0.001460164603554397</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4660373893234381</v>
+        <v>0.3229428877413782</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001201926509768414</v>
+        <v>0.0008273631101851133</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4663187293645495</v>
+        <v>0.3231352369128624</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000455352738427235</v>
+        <v>0.0003120796922840649</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4660250008456575</v>
+        <v>0.3229313677799522</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002107882469095697</v>
+        <v>0.0001436296598611833</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4659908971430587</v>
+        <v>0.322906321862346</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.41178788466895e-05</v>
+        <v>4.909079472171628e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4659281636383566</v>
+        <v>0.3228615570089519</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.837230183129111e-05</v>
+        <v>1.121751555640607e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4658907149811089</v>
+        <v>0.3228340416141267</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.447658039816054e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4658856971097</v>
+        <v>0.3228290289552121</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>-8.904788376657899e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4658816063571128</v>
+        <v>0.3228246473696513</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.465878988953694</v>
+        <v>0.3228212970148586</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4658734717117043</v>
+        <v>0.3228159276878708</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4658671477176964</v>
+        <v>0.3228099349544404</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.465861779929118</v>
+        <v>0.3228045671658621</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4658618166776097</v>
+        <v>0.3228046039143538</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4658619269230853</v>
+        <v>0.3228047141598293</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4658620004200689</v>
+        <v>0.3228047876568129</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.465862184162528</v>
+        <v>0.3228049713992721</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4658637275991845</v>
+        <v>0.3228065148359286</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4658651975388576</v>
+        <v>0.3228079847756016</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4658664469875796</v>
+        <v>0.3228092342243237</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4658678066817769</v>
+        <v>0.322810593918521</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4658656017722676</v>
+        <v>0.3228083890090117</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8622438452578778</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4658651975388576</v>
+        <v>0.3228079847756016</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4658643523235456</v>
+        <v>0.3228071395602897</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4658649035509229</v>
+        <v>0.322807690787667</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4658645728144964</v>
+        <v>0.3228073600512406</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.465864278826562</v>
+        <v>0.3228070660633061</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4658643523235456</v>
+        <v>0.3228071395602897</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4658639113416437</v>
+        <v>0.3228066985783877</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4658638010961681</v>
+        <v>0.3228065883329122</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4658637643476764</v>
+        <v>0.3228065515844205</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4658639113416437</v>
+        <v>0.3228066985783877</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.46586343361125</v>
+        <v>0.3228062208479941</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4658643890720373</v>
+        <v>0.3228071763087814</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4658643523235456</v>
+        <v>0.3228071395602897</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4658640215871192</v>
+        <v>0.3228068088238633</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4658644625690211</v>
+        <v>0.3228072498057653</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4658638378446601</v>
+        <v>0.3228066250814041</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4658636541022009</v>
+        <v>0.3228064413389449</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4658632498687909</v>
+        <v>0.3228060371055349</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4658624046534789</v>
+        <v>0.3228051918902229</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4658623679049872</v>
+        <v>0.3228051551417312</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4658625148989544</v>
+        <v>0.3228053021356985</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4658624414019708</v>
+        <v>0.3228052286387149</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4658625148989544</v>
+        <v>0.3228053021356985</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4658625516474463</v>
+        <v>0.3228053388841904</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4658624414019708</v>
+        <v>0.3228052286387149</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4658628823838727</v>
+        <v>0.3228056696206169</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4658627721383972</v>
+        <v>0.3228055593751413</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4658627353899053</v>
+        <v>0.3228055226266494</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4658626618929216</v>
+        <v>0.3228054491296657</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.46586262514443</v>
+        <v>0.3228054123811741</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4658624046534789</v>
+        <v>0.3228051918902229</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4658623311564953</v>
+        <v>0.3228051183932393</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4658622576595116</v>
+        <v>0.3228050448962557</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4658622944080036</v>
+        <v>0.3228050816447476</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.465862184162528</v>
+        <v>0.3228049713992721</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4658622944080036</v>
+        <v>0.3228050816447476</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.465862588395938</v>
+        <v>0.3228053756326821</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_3_000008.xlsx
+++ b/out/LSTM-S4_repeat_3_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.01414979196763896</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.986393030374176</v>
+        <v>0.01414979196763896</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8622438452578778</v>
+        <v>0.01414979196763896</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8622438452578778</v>
+        <v>-0.6369672081768306</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.6369672081768306</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.386393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001316227959683165</v>
+        <v>-0.0001254644500103313</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1512093120794342</v>
+        <v>-0.1441345553929944</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1442600198430048</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1442600198430048</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1442600198430048</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1442600198430048</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1442600198430048</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1442600198430048</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1442600198430048</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1442600198430048</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1442600198430048</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1442600198430048</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1442600198430048</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1442600198430048</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1513409348754025</v>
+        <v>-0.1442600198430048</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1514554797617658</v>
+        <v>-0.1443696920922732</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4118773248406163</v>
+        <v>0.3943564315444599</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6730899894655917</v>
+        <v>0.6451003497860499</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02934613633254492</v>
+        <v>0.02809781295007468</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3192443141875116</v>
+        <v>0.3063069531403945</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05146312427903974</v>
+        <v>0.04927399039631967</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3928148166683598</v>
+        <v>0.3767477440903138</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06252193003882106</v>
+        <v>0.05986176733290857</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.386393030374176</v>
+        <v>0.4652667921121083</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4663903990595937</v>
+        <v>0.4471932240622027</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01654486918756538</v>
+        <v>0.01584092348467946</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.4652667921121084</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4368783834454406</v>
+        <v>0.4189365820836886</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009191027858687134</v>
+        <v>0.00879994169825625</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.386393030374176</v>
+        <v>0.4652667921121084</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4387003097358528</v>
+        <v>0.420680813351936</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01931219112348164</v>
+        <v>0.01849088753544879</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4681450155157126</v>
+        <v>0.4488733027286469</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007583587329954639</v>
+        <v>0.007261441745886984</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.986393030374176</v>
+        <v>0.4652667921121084</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.463984703571344</v>
+        <v>0.4448897059767074</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005399221778498081</v>
+        <v>0.005169805405520028</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4671969123559822</v>
+        <v>0.4479648473483184</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002122815508591047</v>
+        <v>0.002031836798268392</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4660373893234381</v>
+        <v>0.4468546880957238</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001201926509768414</v>
+        <v>0.001151059875257102</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4663187293645495</v>
+        <v>0.4471237841672296</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000455352738427235</v>
+        <v>0.0004353884615056456</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4660250008456575</v>
+        <v>0.4468425770381875</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002107882469095697</v>
+        <v>0.0002008796029188242</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4659908971430587</v>
+        <v>0.4468097362331124</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.41178788466895e-05</v>
+        <v>7.088857766927358e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4659281636383566</v>
+        <v>0.44674935919799</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.837230183129111e-05</v>
+        <v>1.741833032797311e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4658907149811089</v>
+        <v>0.446713234975732</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.447658039816054e-06</v>
+        <v>5.970672288157051e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4658856971097</v>
+        <v>0.446708217848965</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4658816063571128</v>
+        <v>0.4467040903478861</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.465878988953694</v>
+        <v>0.4467012892020084</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4658734717117043</v>
+        <v>0.446695845457002</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4658671477176964</v>
+        <v>0.4466898527235717</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.465861779929118</v>
+        <v>0.4466844849349933</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4658618166776097</v>
+        <v>0.446684521683485</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4658619269230853</v>
+        <v>0.4466846319289606</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4658620004200689</v>
+        <v>0.4466847054259442</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.465862184162528</v>
+        <v>0.4466848891684033</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.01414979196763891</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4658637275991845</v>
+        <v>0.4466864326050598</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4658651975388576</v>
+        <v>0.4466879025447329</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4658664469875796</v>
+        <v>0.4466891519934549</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4658678066817769</v>
+        <v>0.4466905116876522</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.986393030374176</v>
+        <v>0.6652667921121085</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4658656017722676</v>
+        <v>0.4466883067781429</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8622438452578778</v>
+        <v>0.01414979196763883</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4658651975388576</v>
+        <v>0.4466879025447329</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4658643523235456</v>
+        <v>0.4466870573294209</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4658649035509229</v>
+        <v>0.4466876085567982</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4658645728144964</v>
+        <v>0.4466872778203718</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.465864278826562</v>
+        <v>0.4466869838324373</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4658643523235456</v>
+        <v>0.4466870573294209</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4658639113416437</v>
+        <v>0.446686616347519</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4658638010961681</v>
+        <v>0.4466865061020434</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4658637643476764</v>
+        <v>0.4466864693535517</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4658639113416437</v>
+        <v>0.446686616347519</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.46586343361125</v>
+        <v>0.4466861386171254</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4658643890720373</v>
+        <v>0.4466870940779126</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4658643523235456</v>
+        <v>0.4466870573294209</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4658640215871192</v>
+        <v>0.4466867265929945</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4658644625690211</v>
+        <v>0.4466871675748965</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4658638378446601</v>
+        <v>0.4466865428505354</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4658636541022009</v>
+        <v>0.4466863591080762</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4658632498687909</v>
+        <v>0.4466859548746662</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4658624046534789</v>
+        <v>0.4466851096593542</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4658623679049872</v>
+        <v>0.4466850729108625</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4658625148989544</v>
+        <v>0.4466852199048297</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4658624414019708</v>
+        <v>0.4466851464078461</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4658625148989544</v>
+        <v>0.4466852199048297</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4658625516474463</v>
+        <v>0.4466852566533216</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4658624414019708</v>
+        <v>0.4466851464078461</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4658628823838727</v>
+        <v>0.4466855873897481</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4658627721383972</v>
+        <v>0.4466854771442725</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4658627353899053</v>
+        <v>0.4466854403957806</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4658626618929216</v>
+        <v>0.446685366898797</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.46586262514443</v>
+        <v>0.4466853301503053</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4658624046534789</v>
+        <v>0.4466851096593542</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4658623311564953</v>
+        <v>0.4466850361623706</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4658622576595116</v>
+        <v>0.446684962665387</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4658622944080036</v>
+        <v>0.4466849994138789</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.465862184162528</v>
+        <v>0.4466848891684033</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4658622944080036</v>
+        <v>0.4466849994138789</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.465862588395938</v>
+        <v>0.4466852934018133</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_3_000008.xlsx
+++ b/out/LSTM-S4_repeat_3_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.006485726684331894</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.003724932670593262</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.5799999999999996</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.001483000814914703</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.0001849904656410217</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.1858502080323611</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0002007484436035156</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.1858502080323611</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001024045050144196</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.001513998955488205</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.001931097358465195</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.001783419400453568</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.001610022038221359</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.001213725656270981</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0007365047931671143</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0002801194787025452</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-1.117587089538574e-05</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.01414979196763896</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0003599226474761963</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.01414979196763896</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-2.674758434295654e-05</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.01414979196763896</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0004443861544132233</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6369672081768306</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.000566430389881134</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6369672081768306</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.0004594996571540833</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.0002096444368362427</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>3.315135836601257e-05</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0003625191748142242</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.316383792256578</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0006316900253295898</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001143436878919601</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.001334108412265778</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.001278553158044815</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001323655247688293</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.001549381762742996</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.00207153707742691</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.002585466951131821</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.003917600959539413</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.116383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.003650769591331482</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.116383792256578</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.003207094967365265</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.116383792256578</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.003126867115497589</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.116383792256578</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002822991460561752</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.116383792256578</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.00279531255364418</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.002541549503803253</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.002391330897808075</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.002976894378662109</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.003671117126941681</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.116383792256578</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.00403614342212677</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.116383792256578</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.004375077784061432</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.116383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.005136873573064804</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.116383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.005515456199645996</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.116383792256578</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001254644500103313</v>
+        <v>-0.0001196160965063609</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1441345553929944</v>
+        <v>-0.1374159204966616</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.003833554685115814</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.116383792256578</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1442600198430048</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.002707958221435547</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1442600198430048</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.001368332654237747</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1442600198430048</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.0006820559501647949</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1442600198430048</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.0002410188317298889</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1442600198430048</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.0002420321106910706</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1442600198430048</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.0003973059356212616</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1442600198430048</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.0009928420186042786</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1442600198430048</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.001355715095996857</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1442600198430048</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.001526877284049988</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1442600198430048</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.001310557126998901</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1442600198430048</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.0009726546704769135</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1442600198430048</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.0009603202342987061</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1442600198430048</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.001642171293497086</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1443696920922732</v>
+        <v>-0.1376000274538506</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3943564315444599</v>
+        <v>0.2318944478277541</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.001229386776685715</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6451003497860499</v>
+        <v>0.3266341140331705</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02809781295007468</v>
+        <v>0.01652243072011493</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0009284168481826782</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3063069531403945</v>
+        <v>0.1274125434982516</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04927399039631967</v>
+        <v>0.02897458562240291</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.001137629151344299</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3767477440903138</v>
+        <v>0.168834027043551</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05986176733290857</v>
+        <v>0.03520069965981258</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.0005864761769771576</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4652667921121083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4471932240622027</v>
+        <v>0.2102584512785005</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01584092348467946</v>
+        <v>0.009313996799435066</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.0003741234540939331</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4652667921121084</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4189365820836886</v>
+        <v>0.1936414995474231</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.00879994169825625</v>
+        <v>0.005172672591145436</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.0005721375346183777</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4652667921121084</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.420680813351936</v>
+        <v>0.1946651204177889</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01849088753544879</v>
+        <v>0.01087121130641881</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.001312263309955597</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4488733027286469</v>
+        <v>0.2112420495586081</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007261441745886984</v>
+        <v>0.004267667746581547</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.0009762495756149292</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.4652667921121084</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4448897059767074</v>
+        <v>0.2088973039320414</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005169805405520028</v>
+        <v>0.003037785578445776</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.0001538731157779694</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4479648473483184</v>
+        <v>0.2107039415374342</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002031836798268392</v>
+        <v>0.001192660037381815</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.0008826181292533875</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4468546880957238</v>
+        <v>0.2100487404119903</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001151059875257102</v>
+        <v>0.0006747632066511759</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.00192733108997345</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4471237841672296</v>
+        <v>0.210205092644495</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004353884615056456</v>
+        <v>0.0002545355999806605</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.002835270017385483</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4468425770381875</v>
+        <v>0.2100373145764458</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002008796029188242</v>
+        <v>0.0001161056487757789</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.003558050841093063</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4468097362331124</v>
+        <v>0.2100159073688202</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.088857766927358e-05</v>
+        <v>3.940289118946859e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.003976404666900635</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.44674935919799</v>
+        <v>0.209978211924165</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.741833032797311e-05</v>
+        <v>8.355601046452064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.004125088453292847</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.446713234975732</v>
+        <v>0.2099546698343093</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.970672288157051e-06</v>
+        <v>1.677800523226032e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.003944296389818192</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.446708217848965</v>
+        <v>0.2099496594093207</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.00339735671877861</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4467040903478861</v>
+        <v>0.2099451683670245</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-2.908363659633048e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.003423165529966354</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4467012892020084</v>
+        <v>0.2099414515365448</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.003582872450351715</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.446695845457002</v>
+        <v>0.2099361557065407</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.003696754574775696</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4466898527235717</v>
+        <v>0.209930493709537</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003472421318292618</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4466844849349933</v>
+        <v>0.2099303099670778</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.003155551850795746</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.446684521683485</v>
+        <v>0.2099303467155695</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.00277053564786911</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4466846319289606</v>
+        <v>0.209930456961045</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.002637282013893127</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4466847054259442</v>
+        <v>0.2099305304580287</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.00187547504901886</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.16</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4466848891684033</v>
+        <v>0.2099307142004878</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.0001008808612823486</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.01414979196763891</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4466864326050598</v>
+        <v>0.2099322576371443</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.0003057941794395447</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4466879025447329</v>
+        <v>0.2099337275768174</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0005369894206523895</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4466891519934549</v>
+        <v>0.2099349770255394</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.003493469208478928</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.316383792256578</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4466905116876522</v>
+        <v>0.2099363367197367</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.001216109842061996</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.6652667921121085</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4466883067781429</v>
+        <v>0.2099341318102274</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.001363698393106461</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.01414979196763883</v>
+        <v>0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4466879025447329</v>
+        <v>0.2099337275768174</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.003654439002275467</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4466870573294209</v>
+        <v>0.2099328823615054</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.005748428404331207</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4466876085567982</v>
+        <v>0.2099334335888827</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.007161874324083328</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4466872778203718</v>
+        <v>0.2099331028524563</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.007446069270372391</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4466869838324373</v>
+        <v>0.2099328088645218</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.007552802562713623</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4466870573294209</v>
+        <v>0.2099328823615054</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.007768839597702026</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.446686616347519</v>
+        <v>0.2099324413796035</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.007669024169445038</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4466865061020434</v>
+        <v>0.2099323311341279</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.007067441940307617</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4466864693535517</v>
+        <v>0.2099322943856362</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.007232014089822769</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.446686616347519</v>
+        <v>0.2099324413796035</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.005884602665901184</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4466861386171254</v>
+        <v>0.2099319636492098</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.004550132900476456</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4466870940779126</v>
+        <v>0.2099329191099971</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.005718424916267395</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4466870573294209</v>
+        <v>0.2099328823615054</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.007007081061601639</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4466867265929945</v>
+        <v>0.209932551625079</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.007955092936754227</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4466871675748965</v>
+        <v>0.209932992606981</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.008717499673366547</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4466865428505354</v>
+        <v>0.2099323678826198</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.008964478969573975</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4466863591080762</v>
+        <v>0.2099321841401607</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.009094573557376862</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4466859548746662</v>
+        <v>0.2099317799067507</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.009196892380714417</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4466851096593542</v>
+        <v>0.2099309346914387</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.009201414883136749</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4466850729108625</v>
+        <v>0.209930897942947</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.008877474814653397</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4466852199048297</v>
+        <v>0.2099310449369142</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.008479345589876175</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4466851464078461</v>
+        <v>0.2099309714399306</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.007530301809310913</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4466852199048297</v>
+        <v>0.2099310449369142</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.007779177278280258</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4466852566533216</v>
+        <v>0.2099310816854062</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.007124654948711395</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4466851464078461</v>
+        <v>0.2099309714399306</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.007348928600549698</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4466855873897481</v>
+        <v>0.2099314124218326</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.00743875652551651</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4466854771442725</v>
+        <v>0.209931302176357</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.007719025015830994</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4466854403957806</v>
+        <v>0.2099312654278651</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.007662929594516754</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.446685366898797</v>
+        <v>0.2099311919308815</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.007365051656961441</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4466853301503053</v>
+        <v>0.2099311551823898</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.007311243563890457</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4466851096593542</v>
+        <v>0.2099309346914387</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.006598088890314102</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4466850361623706</v>
+        <v>0.2099308611944551</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.005952257663011551</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.446684962665387</v>
+        <v>0.2099307876974714</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.005623705685138702</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4466849994138789</v>
+        <v>0.2099308244459634</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.004923120141029358</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4466848891684033</v>
+        <v>0.2099307142004878</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.00378543883562088</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4466849994138789</v>
+        <v>0.2099308244459634</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003190785646438599</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4466852934018133</v>
+        <v>0.2099311184338979</v>
       </c>
     </row>
   </sheetData>
